--- a/outputs/divergencias/divergencias_ipea.xlsx
+++ b/outputs/divergencias/divergencias_ipea.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos construção civil - í..." sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produção automóveis" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rendimento nominal poupança ..." sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo de crédito pessoas fís..." sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,20 +498,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C3" t="n">
         <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>✔️ OK</t>
+          <t>❌ 4 divergência(s)</t>
         </is>
       </c>
     </row>
@@ -836,11 +837,11 @@
         <v>2026</v>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>mensal</t>
@@ -848,7 +849,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>✔️ Atualizada (2 mês(es) de defasagem)</t>
+          <t>✔️ Atualizada (1 mês(es) de defasagem)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4447,6 +4448,120 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
+        <is>
+          <t>Período ausente no Cognos</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C139" t="n">
+        <v>11</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4382025</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4382704</v>
+      </c>
+      <c r="F139" t="n">
+        <v>679</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.01549271865040395</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C140" t="n">
+        <v>12</v>
+      </c>
+      <c r="D140" t="n">
+        <v>4430415</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4428977</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.03246799430207021</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4466950</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4460716</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6234</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.1397533490139251</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4491912</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
         <is>
           <t>Período ausente no Cognos</t>
         </is>
@@ -7963,4 +8078,174 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Valor API</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Cognos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Diferença Absoluta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Diferença Relativa (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4382025</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4382704</v>
+      </c>
+      <c r="F2" t="n">
+        <v>679</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01549271865040395</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4430415</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4428977</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03246799430207021</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4466950</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4460716</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1397533490139251</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Valores diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saldo de crédito pessoas físicas</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4491912</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Período ausente no Cognos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>